--- a/inst/resources/tool_obs_latrine_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_latrine_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$67</definedName>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF149"/>
+  <dimension ref="A1:Z149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -830,7 +830,21 @@
           <t>start</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>début</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>البداية</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>start</t>
@@ -851,7 +865,21 @@
           <t>end</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>النهاية</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>end</t>
@@ -872,7 +900,21 @@
           <t>today</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>aujourd’hui</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اليوم</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>today</t>
@@ -893,7 +935,21 @@
           <t>deviceid</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>identifiant de l’appareil</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>معرّف الجهاز</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>identificador del dispositivo</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>deviceid</t>
@@ -914,7 +970,21 @@
           <t>audit</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>journal d’audit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>registro de auditoría</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>audit</t>
@@ -941,9 +1011,21 @@
           <t>date_survey</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la date de l’observation ?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ما هو تاريخ الملاحظة؟</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuál es la fecha de la observación?</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -978,8 +1060,21 @@
           <t>enumerator</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer l’identifiant de l’enquêteur</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تحديد معرف الباحث الميداني</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Por favor indique el identificador del encuestador</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Please specify enumerator ID</t>
@@ -1003,8 +1098,21 @@
           <t>contact_WASH</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Contact du partenaire ONG WASH</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>جهة الاتصال لدى شريك منظمة المياه والصرف الصحي والنظافة</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Contacto del socio ONG WASH</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Contact for WASH NGO Partner</t>
@@ -1028,8 +1136,21 @@
           <t>contact_water</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Contact du comité de gestion de l’eau</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>جهة الاتصال لدى لجنة إدارة المياه</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Contacto del comité de gestión del agua</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Contact for Water Management Committees</t>
@@ -1053,21 +1174,34 @@
           <t>gps_coordinates</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Veuillez fournir les coordonnées GPS du lieu de l’observation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(Appuyer sur l'icône de détection de la position actuelle)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n"/>
+          <t>(Appuyez sur l’icône pour détecter la position actuelle)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تقديم إحداثيات GPS لموقع الملاحظة</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(انقر على أيقونة اكتشاف الموقع الحالي)</t>
+          <t>(اضغط على أيقونة تحديد الموقع الحالي)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Por favor proporcione las coordenadas GPS del lugar de la observación</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(Toca el icono para detectar la ubicación actual)</t>
+          <t>(Toque el icono para detectar la ubicación actual)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1098,8 +1232,21 @@
           <t>time</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Heure de l’observation</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>وقت الملاحظة</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hora de la observación</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Time of Observation</t>
@@ -1144,8 +1291,21 @@
           <t>name</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le nom du point de latrines ?</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نقطة المراحيض؟</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>¿Cuál es el nombre del punto de letrinas?</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>What is the name of the Latrine point?</t>
@@ -1169,8 +1329,21 @@
           <t>type_latrine</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le type d’infrastructure de latrine ?</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ما نوع بنية المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>¿Qué tipo de infraestructura de letrina es?</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>What is the type of latrine infrastructure?</t>
@@ -1194,9 +1367,22 @@
           <t>type_latrine_other</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1225,8 +1411,21 @@
           <t>type_usage</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Quel est le type d’utilisation de cette latrine ?</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ما نوع استخدام هذا المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>¿Cuál es el tipo de uso de esta letrina?</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>What is the usage type of this latrine?</t>
@@ -1250,9 +1449,22 @@
           <t>type_usage_other</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1281,8 +1493,21 @@
           <t>latrine_block</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>La latrine fait-elle partie d’un bloc de latrines ?</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>هل المرحاض جزء من كتلة مراحيض؟</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>¿La letrina forma parte de un bloque?</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Is the latrine part of a block?</t>
@@ -1306,9 +1531,22 @@
           <t>latrines_per_block</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, combien de latrines y a-t-il par bloc ?</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، كم عدد المراحيض في كل كتلة؟</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿cuántas letrinas hay por bloque?</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>If yes, how many latrines per block?</t>
@@ -1337,8 +1575,21 @@
           <t>latrine_gender_seg</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>La latrine / le bloc est-il séparé par sexe ?</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>هل المرحاض/الكتلة منفصل حسب الجنس؟</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>¿La letrina/bloque está separado por sexo?</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Is the latrine / block gender segregated?</t>
@@ -1362,9 +1613,22 @@
           <t>latrine_gender_marked</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, la latrine est-elle clairement indiquée comme étant destinée aux femmes ou aux hommes ?</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، هل المرحاض محدد بوضوح للنساء أو للرجال؟</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿la letrina está claramente señalizada para mujeres u hombres?</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>If yes, is the latrine clearly marked as for women or male?</t>
@@ -1393,9 +1657,22 @@
           <t>latrine_genders</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, la latrine observée est-elle réservée aux femmes ou aux hommes ?</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، هل المرحاض الذي تمت ملاحظته مخصص للنساء أم للرجال؟</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿la letrina observada está reservada para mujeres u hombres?</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>If yes, is the observed latrine reserved to women or to men?</t>
@@ -1424,8 +1701,21 @@
           <t>note_features</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="F24" s="2" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** La latrine observée dispose-t-elle des éléments suivants ? **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** هل يحتوي المرحاض الذي تمت ملاحظته على العناصر التالية؟ **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** ¿La letrina observada tiene los siguientes elementos? **&lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;** Does the observed latrine have the following features?**&lt;/span&gt;</t>
@@ -1449,8 +1739,21 @@
           <t>latrine_door</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Porte</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>باب</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Puerta</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Door</t>
@@ -1479,8 +1782,21 @@
           <t>latrine_roof</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Toit</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>سقف</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Techo</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Roof</t>
@@ -1509,8 +1825,21 @@
           <t>latrine_walls_privacy</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Murs assurant l’intimité</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>جدران توفر الخصوصية</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paredes que garantizan privacidad</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Walls that protect privacy</t>
@@ -1539,8 +1868,21 @@
           <t>latrine_lock</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Verrou pour fermer la porte</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>قفل لإغلاق الباب</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cerradura para cerrar la puerta</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Lock to close door</t>
@@ -1569,8 +1911,21 @@
           <t>latrine_light_in</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Éclairage intérieur</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>إضاءة داخلية</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Luz interior</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Inside light</t>
@@ -1599,8 +1954,21 @@
           <t>latrine_light_out</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Éclairage extérieur</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>إضاءة خارجية</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Luz exterior</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Outside light</t>
@@ -1629,8 +1997,21 @@
           <t>latrine_ventilation</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Ventilation</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>تهوية</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ventilación</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Ventilation</t>
@@ -1654,9 +2035,36 @@
           <t>latrine_walls</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>De quel matériau sont faits les murs de la latrine ?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>من أي مادة صُنعت جدران المرحاض؟</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>¿De qué material están hechas las paredes de la letrina?</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>What material are the walls of the latrine made of?</t>
@@ -1685,9 +2093,22 @@
           <t>latrine_walls_other</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1716,8 +2137,21 @@
           <t>slab_material</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>S’il y a une dalle, de quel matériau est-elle faite ?</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت هناك أرضية/بلاطة، من أي مادة صُنعت؟</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Si tiene losa, ¿de qué material está hecha?</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>If has slab, what material is the slab made of?</t>
@@ -1741,9 +2175,22 @@
           <t>slab_material_other</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1772,8 +2219,21 @@
           <t>visible_damage</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="F36" s="2" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Observe-t-on des signes de dommage, d’inachèvement ou de mauvais entretien de la latrine ?</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد أي علامات مرئية على تلف أو عدم اكتمال أو سوء صيانة المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>¿Hay signos observables de daño, falta de terminación o mal mantenimiento de la letrina?</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Is there any observable signs of damage, incompleteness or poor maintenance of the latrine?</t>
@@ -1797,10 +2257,36 @@
           <t>damage</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Qu’est-ce qui est endommagé, incomplet ou mal entretenu ?</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>ما الجزء المتضرر أو غير المكتمل أو سيئ الصيانة؟</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>¿Qué está dañado, incompleto o mal mantenido?</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>what is damaged, incomplete or poorly maintained?</t>
@@ -1834,9 +2320,22 @@
           <t>damage_other</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1865,8 +2364,21 @@
           <t>visibly_clean</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n"/>
-      <c r="F39" s="2" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>La latrine est-elle visiblement propre ?</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>هل المرحاض نظيف بشكل واضح؟</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>¿La letrina está visiblemente limpia?</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Is the latrine visibly clean?</t>
@@ -1890,10 +2402,36 @@
           <t>clean_issues</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Si elle n’est pas propre, observez-vous l’un des problèmes suivants ?</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>إذا لم يكن نظيفاً، هل تلاحظ أياً من هذه المشاكل؟</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Si no está limpia, ¿observa alguno de estos problemas?</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">If not clean, do you observe any of these issues: </t>
@@ -1927,9 +2465,22 @@
           <t>clean_issues_other</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1958,9 +2509,36 @@
           <t>latrine_full</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>La latrine est-elle pleine ?</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Utilisez une lampe et éclairez l’intérieur de la latrine pour vérifier</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>هل المرحاض ممتلئ؟</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>استخدم مصباحاً وسلّط الضوء داخل المرحاض للتحقق</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>¿La letrina está llena?</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Use una luz e ilumine dentro de la letrina para verificar</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Is the latrine full?</t>
@@ -1989,8 +2567,22 @@
           <t>technical_knowledge</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Nous souhaitons maintenant poser des questions complémentaires sur le dispositif de confinement. Disposez-vous de connaissances WASH/techniques suffisantes pour identifier ce qu’est un dispositif de confinement et reconnaître les problèmes de base liés au confinement ?</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>نود الآن طرح أسئلة إضافية حول نظام الاحتواء. هل لديك معرفة تقنية/في مجال المياه والصرف الصحي والنظافة كافية لتحديد ما هو نظام الاحتواء والتعرف على مشاكله الأساسية؟</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ahora quisiéramos hacer preguntas complementarias sobre el sistema de contención. ¿Tiene conocimientos técnicos/WASH suficientes para identificar qué es un sistema de contención y reconocer problemas básicos de contención?</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Now we would like to ask supplemental questions about the containement. Do you have sufficient WASH/technical knowledge to identify what is a containment and recognize basic containment issues?</t>
@@ -2016,7 +2608,21 @@
           <t>note_containment</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** Questions sur le confinement (complémentaires) **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** أسئلة حول الاحتواء (إضافية) **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** Preguntas sobre contención (complementarias) **&lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;**Containement questions (supplemental)**&lt;/span&gt;</t>
@@ -2037,10 +2643,36 @@
           <t>outlet_pipe</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Le dispositif de confinement (fosse ou réservoir) dispose-t-il d’un tuyau de sortie pour les effluents liquides ?</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>La sortie est un tuyau externe par lequel les effluents liquides du dispositif de confinement sont évacués</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>هل يحتوي نظام الاحتواء (خزان أو حفرة) على أنبوب مخرج للسوائل الخارجة؟</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>المخرج هو أنبوب خارجي يتم من خلاله تصريف السوائل الخارجة من نظام الاحتواء</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>¿El sistema de contención (tanque o fosa) tiene una tubería de salida para efluentes líquidos?</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>La salida es una tubería externa por la cual se descarga el efluente líquido del sistema de contención</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Does the containment (tank or pit) have an outlet pipe for liquid effluent?</t>
@@ -2074,9 +2706,22 @@
           <t>outlet_pipe_discharge_location</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Si le dispositif de confinement dispose d’un tuyau de sortie pour les effluents liquides, où ce tuyau se déverse-t-il ?</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>إذا كان نظام الاحتواء يحتوي على أنبوب مخرج للسوائل، فأين يصرف هذا الأنبوب؟</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Si el sistema de contención tiene una tubería de salida para efluentes líquidos, ¿dónde descarga esa tubería?</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>If the containment has an outlet pipe for liquid effluent, where does this pipe discharge?</t>
@@ -2105,9 +2750,22 @@
           <t>discharge_where_other</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -2136,10 +2794,36 @@
           <t>containement_issues</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="H48" s="10" t="n"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Observez le dispositif de confinement. Y a-t-il des problèmes visibles qui empêchent le confinement correct des excréta ?</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>راقب نظام الاحتواء. هل توجد أي مشاكل مرئية في المرفق تؤدي إلى عدم احتواء الفضلات بشكل صحيح؟</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Observe el sistema de contención. ¿Hay problemas visibles en la instalación que impidan contener adecuadamente las excretas?</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Observe the containement. Is there are any visible problems with the facility causing excreta to not be contained?</t>
@@ -2173,8 +2857,21 @@
           <t>containment_water</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="F49" s="2" t="n"/>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>L’eau (souterraine) peut-elle entrer ou sortir de la fosse / fosse septique ? (c’est-à-dire que la fosse n’est pas étanche ou scellée)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>هل يمكن للمياه (الجوفية) الدخول إلى الحفرة/خزان الصرف أو الخروج منه؟ (أي أن الحفرة/الخزان غير محكم أو غير مغلق)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>¿Puede entrar o salir agua (subterránea) de la fosa/tanque séptico? (es decir, la fosa/tanque no es hermético ni está sellado)</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">Can (ground) water get in or out of the pit/septic tank? (so the pit/septic tank is not "water tight or sealed") </t>
@@ -2198,9 +2895,22 @@
           <t>drainage_channel</t>
         </is>
       </c>
-      <c r="D50" s="9" t="n"/>
-      <c r="F50" s="2" t="n"/>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Existe-t-il un canal de drainage de protection dans la latrine / le bloc ?</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد قناة تصريف وقائية داخل المرحاض/الكتلة؟</t>
+        </is>
+      </c>
       <c r="G50" s="9" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>¿Hay un canal de drenaje de protección dentro de la letrina/bloque?</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Is there a protective drainage channel within the latrine / block?</t>
@@ -2229,8 +2939,21 @@
           <t>handwashing_station</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il un poste de lavage des mains avec eau et savon au niveau de la latrine ?</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد محطة لغسل اليدين بالماء والصابون عند المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>¿Hay una estación de lavado de manos con agua y jabón en la letrina?</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Is there a handwashing station with soap and water at the latrine?</t>
@@ -2254,9 +2977,36 @@
           <t>note_environmental_threat</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** Observez-vous l’un des éléments suivants autour de la latrine ? **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** هل تلاحظ أياً من العناصر التالية حول المرحاض؟ **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;** ¿Observa alguno de los siguientes elementos alrededor de la letrina? **&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;**Do you observe any of the following elements around the latrine?**&lt;/span&gt;</t>
@@ -2290,8 +3040,21 @@
           <t>animals_latrine</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Animaux, nuisibles ou rongeurs autour de la latrine ?</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد حيوانات أو آفات أو قوارض حول المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>¿Hay animales, plagas o roedores alrededor de la letrina?</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Animals, pests or rodents around the latrine?</t>
@@ -2320,8 +3083,21 @@
           <t>solid_waste</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n"/>
-      <c r="F54" s="2" t="n"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Déchets solides</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>نفايات صلبة</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Residuos sólidos</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Solid waste</t>
@@ -2350,8 +3126,21 @@
           <t>faeces</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Fèces humaines ou animales, ou traces de fèces</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>براز بشري أو حيواني أو آثار براز</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Heces humanas o animales, o rastros de heces</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Human or animal faeces or traces of faeces</t>
@@ -2380,8 +3169,21 @@
           <t>effluents</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n"/>
-      <c r="F56" s="2" t="n"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Effluents visibles, eaux usées, eaux d’égout, etc.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>سوائل ملوثة مرئية، مياه عادمة، صرف صحي، إلخ</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Efluentes visibles, aguas residuales, alcantarillado, etc.</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Visible effluents, waste water, sewage, etc.</t>
@@ -2410,8 +3212,21 @@
           <t>soil_charac</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n"/>
-      <c r="F57" s="2" t="n"/>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Quelles sont les caractéristiques du sol autour de la latrine ?</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>ما هي خصائص التربة حول المرحاض؟</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>¿Cuáles son las características del suelo alrededor de la letrina?</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>What’s the characteristic of the soil around the latrine?</t>
@@ -2435,9 +3250,22 @@
           <t>soil_charac_other</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -2466,8 +3294,21 @@
           <t>latrine_distance</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>La latrine se trouve-t-elle à moins de 30 mètres d’une source d’eau ?</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>هل يقع المرحاض على بعد أقل من 30 متراً من أي مصدر مياه؟</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>¿La letrina está a menos de 30 metros de alguna fuente de agua?</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Is the latrine within 30 meters of any water source?</t>
@@ -2491,9 +3332,22 @@
           <t>distance_meters</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, à quelle distance &lt;span style="color:red"&gt;en mètres&lt;/span&gt; ?</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما المسافة &lt;span style="color:red"&gt;بالمتر&lt;/span&gt;؟</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿a qué distancia &lt;span style="color:red"&gt;en metros&lt;/span&gt;?</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>If yes, how far &lt;span style="color:red"&gt;in meters&lt;/span&gt;?</t>
@@ -2522,8 +3376,21 @@
           <t>distance_dwelling</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n"/>
-      <c r="F61" s="2" t="n"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>La latrine se trouve-t-elle à moins de 50 mètres d’une habitation ?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>هل يقع المرحاض على بعد أقل من 50 متراً من أي مسكن؟</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>¿La letrina está a menos de 50 metros de alguna vivienda?</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Is the latrine within 50 meters of any dwelling?</t>
@@ -2547,9 +3414,22 @@
           <t>distance_dwelling_meters</t>
         </is>
       </c>
-      <c r="D62" s="8" t="n"/>
-      <c r="F62" s="2" t="n"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Si oui, à quelle distance &lt;span style="color:red"&gt;en mètres&lt;/span&gt; se trouve l’habitation la plus proche ?</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما المسافة &lt;span style="color:red"&gt;بالمتر&lt;/span&gt; إلى أقرب مسكن؟</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿a qué distancia &lt;span style="color:red"&gt;en metros&lt;/span&gt; está la vivienda más cercana?</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>If yes, how far &lt;span style="color:red"&gt;in meters&lt;/span&gt; is the closest dwelling?</t>
@@ -2578,7 +3458,21 @@
           <t>note_kii</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Nous souhaitons maintenant poser des questions supplémentaires à un membre du personnel d’une ONG WASH ou à un prestataire de services disposant des connaissances techniques nécessaires et connaissant ces latrines.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>نود الآن طرح أسئلة إضافية على موظف من منظمة WASH أو مقدم خدمة لديه المعرفة التقنية المطلوبة ومطلع على هذه المراحيض.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ahora quisiéramos hacer preguntas adicionales a un miembro del personal de una ONG WASH o proveedor de servicios que tenga los conocimientos técnicos necesarios y esté familiarizado con estas letrinas.</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Now we would like to ask additional question to a WASH NGO staff or service provider who have the required technical knowledge and are familiar with these latrines.</t>
@@ -2599,8 +3493,21 @@
           <t>kii_available</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;Y a-t-il un membre du personnel d’une ONG WASH ou d’un prestataire de services qui peut vous renseigner sur le nombre de personnes utilisant ces latrines et les réhabilitations nécessaires ?&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;هل يوجد موظف من منظمة WASH أو مقدم خدمة يمكنه إخبارك بعدد الأشخاص الذين يستخدمون هذه المراحيض وبأعمال إعادة التأهيل المطلوبة؟&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;¿Hay algún miembro del personal de una ONG WASH o proveedor de servicios que pueda informarle sobre el número de personas que utilizan estas letrinas y la rehabilitación necesaria?&lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;Is there any WASH NGO or service provider staff member who can tell you about the number of people using these latrines and rehabilitation needed? &lt;/span&gt;</t>
@@ -2624,8 +3531,21 @@
           <t>ratio_latrines_people</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le ratio de personnes par latrine ?</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>ما هي نسبة الأشخاص إلى عدد المراحيض؟</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>¿Cuál es la proporción de personas por letrina?</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>What is the ratio of people to latrines?</t>
@@ -2649,8 +3569,21 @@
           <t>rehab_needed</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Une réhabilitation de la latrine est-elle nécessaire ?</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>هل يحتاج المرحاض إلى إعادة تأهيل؟</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>¿Se necesita alguna rehabilitación de la letrina?</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Is any rehabilitation needed for the latrine?</t>
@@ -2674,9 +3607,22 @@
           <t>type_rehab_needed</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quel type de réhabilitation ?</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما نوع إعادة التأهيل؟</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿qué tipo de rehabilitación?</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, what type of rehabilitation? </t>
@@ -2705,7 +3651,21 @@
           <t>comment</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Y a-t-il d’autres commentaires ou observations concernant ce point de latrines ?</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>هل توجد أي تعليقات أو ملاحظات أخرى حول نقطة المراحيض هذه؟</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>¿Hay algún otro comentario u observación sobre este punto de letrinas?</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">Is there any other comment or observation on this latrine point? </t>
@@ -2822,17 +3782,27 @@
     <row r="146"/>
     <row r="147"/>
     <row r="148">
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="C148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="D149" s="2" t="n"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3206,12 +4176,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>رفض الإجابة</t>
+          <t>أفضل عدم الإجابة</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Se niega a responder</t>
+          <t>Prefiere no responder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3996,17 +4966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Chasse d'eau / toilette à versage</t>
+          <t>Toilettes à chasse d’eau ou à chasse manuelle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>مرحاض بالسيفون</t>
+          <t>مرحاض بسحب المياه أو صب المياه</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inodoro de descarga / cisterna</t>
+          <t>Inodoro con descarga o descarga manual</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4029,7 +4999,21 @@
           <t>pit_wo_slab</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Latrine à fosse sans dalle</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>مرحاض حفرة بدون بلاطة</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Letrina de pozo sin losa</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Pit latrine without slab</t>
@@ -4038,7 +5022,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4058,7 +5042,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Latrines à fosse avec dalle</t>
+          <t>Latrine à fosse avec dalle</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>مرحاض حفرة مع بلاطة</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Letrina de pozo con losa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4081,7 +5075,21 @@
           <t>open_hole</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Trou ouvert</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>حفرة مفتوحة</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Agujero abierto</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Open hole</t>
@@ -4104,7 +5112,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Latrines suspendues</t>
+          <t>Latrine / toilette suspendue</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4114,7 +5122,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Letrina / inodoro colgante</t>
+          <t>Letrina / baño colgante</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4139,17 +5147,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Site dédié à la défécation à l'air libre</t>
+          <t>Zone dédiée à la défécation à l’air libre</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>نقطة مخصصة للتغوط في الهواء الطلق</t>
+          <t>مكان مخصص للتبرز في العراء</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Punto de defecación al aire libre dedicado</t>
+          <t>Punto designado de defecación al aire libre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4172,7 +5180,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -4298,7 +5320,21 @@
           <t>plastic</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Plastique</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>بلاستيك</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Plastic</t>
@@ -4356,17 +5392,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Herbe</t>
+          <t>Herbe / chaume</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>عشب</t>
+          <t>عشب / قش</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hierba</t>
+          <t>Hierba / paja</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4389,7 +5425,21 @@
           <t>tin</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Tôle</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>صفيح / ألواح معدنية</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lámina metálica</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Tin</t>
@@ -4445,7 +5495,21 @@
           <t>wood</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Bois</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>خشب</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Wood</t>
@@ -4501,7 +5565,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -4522,7 +5600,21 @@
           <t>no_slab</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Pas de dalle</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>لا توجد بلاطة</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sin losa</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>No slab</t>
@@ -4613,7 +5705,21 @@
           <t>plastic</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Plastique</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>بلاستيك</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>Plastic</t>
@@ -4634,7 +5740,21 @@
           <t>stone</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>حجر</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Piedra</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Stone</t>
@@ -4655,7 +5775,21 @@
           <t>porcelain</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Porcelaine</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>بورسلان</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Porcelana</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Porcelain</t>
@@ -4676,7 +5810,21 @@
           <t>wood</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Bois</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>خشب</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Wood</t>
@@ -4699,17 +5847,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Terre/Sable</t>
+          <t>Terre / sable</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>تراب/رمل</t>
+          <t>تراب / رمل</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tierra/Arena</t>
+          <t>Tierra / arena</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4732,7 +5880,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -4753,7 +5915,21 @@
           <t>yes_fully</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Oui, entièrement fonctionnelle</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>نعم، تعمل بالكامل</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sí, funciona completamente</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>Yes, fully functional</t>
@@ -4774,7 +5950,21 @@
           <t>yes_some</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Oui, partiellement fonctionnelle</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>نعم، تعمل جزئياً</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sí, algunas partes funcionan</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>Yes, some functional</t>
@@ -4795,7 +5985,21 @@
           <t>yes_but_nonfunc</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Oui, mais non fonctionnelle</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>نعم، لكنها لا تعمل</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sí, pero no funciona</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>Yes, but not functional</t>
@@ -4851,7 +6055,21 @@
           <t>unable_to_confirm</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Impossible de confirmer</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>تعذر التأكيد</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>No se puede confirmar</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Unable to confirm</t>
@@ -4872,7 +6090,21 @@
           <t>yes_with_soap</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Oui, avec savon</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>نعم، مع صابون</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sí, con jabón</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes, with soap  </t>
@@ -4893,7 +6125,21 @@
           <t>yes_no_soap</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Oui, sans savon</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>نعم، بدون صابون</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sí, sin jabón</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes, no soap         </t>
@@ -4949,7 +6195,21 @@
           <t>dont_know</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Impossible de confirmer</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>تعذر التأكيد</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No se puede confirmar</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Unable to confirm</t>
@@ -4977,12 +6237,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ممتلئ (100٪)</t>
+          <t>ممتلئة (100٪)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lleno (100%)</t>
+          <t>Llena (100 %)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5012,12 +6272,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>شبه ممتلئ (75٪)</t>
+          <t>شبه ممتلئة (75٪)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casi lleno (75%)</t>
+          <t>Casi llena (75 %)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5052,7 +6312,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Menos lleno (&lt;50%)</t>
+          <t>Menos llena (&lt;50 %)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5075,7 +6335,21 @@
           <t>unable_to_confirm</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Impossible de confirmer</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>تعذر التأكيد</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>No se puede confirmar</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>Unable to confirm</t>
@@ -5096,7 +6370,21 @@
           <t>rock_gravel</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Roche / gravier</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>صخور / حصى</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Roca / grava</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>Rock / Gravel</t>
@@ -5149,10 +6437,24 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">silt_fine </t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n"/>
+          <t>silt_fine</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Limon / terre fine</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>طمي / تربة ناعمة</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Limo / tierra fina</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Silt / Fine Earth</t>
@@ -5173,7 +6475,21 @@
           <t>sand_sediment</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Sable / sédiments</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>رمل / رواسب</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Arena / sedimento</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>Sand / Sediment</t>
@@ -5194,7 +6510,21 @@
           <t>dont_know</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Ne sait pas</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>لا أعرف</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>No sabe</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Don’t Know</t>
@@ -5215,7 +6545,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5243,12 +6587,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>اللوح الغطاء متشقق أو تالف</t>
+          <t>بلاطة الغطاء متشققة أو متضررة</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La losa de cobertura está agrietada o dañada</t>
+          <t>La losa de cubierta está agrietada o dañada</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5271,7 +6615,21 @@
           <t>walls</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Signes indiquant que les murs ne sont pas stables</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>علامات على أن الجدران غير مستقرة</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Señales de que las paredes no son estables</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>Sign walls are not stable</t>
@@ -5292,7 +6650,21 @@
           <t>superstructure</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Superstructure de la latrine (murs, portes, toit, plateforme, etc.) absente, incomplète ou endommagée</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>الهيكل العلوي للمرحاض (الجدران، الأبواب، السقف، المنصة، إلخ) مفقود أو غير مكتمل أو متضرر</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Superestructura de la letrina (paredes, puertas, techo, plataforma, etc.) ausente, incompleta o dañada</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>Toilet superstructure (walls, doors, roof, platform, etc.) absent, incomplete, damaged</t>
@@ -5315,17 +6687,17 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Excréments débordant du trou, de la cuvette ou du piédestal</t>
+          <t>Excréta débordant de l’orifice, de la cuvette ou du siège</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>فيضان الفضلات من فتحة القرفصاء أو الحوض</t>
+          <t>فضلات تفيض من فتحة القرفصاء أو الوعاء أو المقعد</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Excretas desbordando del agujero o cazoleta</t>
+          <t>Excretas desbordando del orificio, taza o pedestal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5348,7 +6720,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5371,7 +6757,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Latrines communales (partagées par plusieurs ménages ou une communauté)</t>
+          <t>Latrine communautaire (partagée par plusieurs ménages ou une communauté)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5381,7 +6767,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Letrina comunal (compartida por varios hogares o una comunidad)</t>
+          <t>Letrina comunitaria (compartida por varios hogares o una comunidad)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5406,17 +6792,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Latrines ménagères (latrines privées pour un ménage)</t>
+          <t>Latrine de ménage (latrine privée pour un ménage)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>مرحاض منزلي (خاص لأسرة واحدة)</t>
+          <t>مرحاض منزلي (مرحاض خاص لأسرة واحدة)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Letrina doméstica (privada para un hogar)</t>
+          <t>Letrina doméstica (letrina privada para un hogar)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5439,7 +6825,21 @@
           <t>public_latrine</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Latrine publique (accessible au grand public)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>مرحاض عام (متاح لعامة الناس)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Letrina pública (accesible al público general)</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>Public latrine (accessible to the general public)</t>
@@ -5462,17 +6862,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Latrines institutionnelles (utilisées par un groupe spécifique, ex. école, centre de santé)</t>
+          <t>Latrine institutionnelle (utilisée par un groupe spécifique, par exemple dans une école ou un établissement de santé)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>مرحاض مؤسسي (مدرسة أو مرفق صحي)</t>
+          <t>مرحاض مؤسسي (تستخدمه فئة محددة، مثل مدرسة أو مرفق صحي، إلخ)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Letrina institucional (escuela, centro de salud, etc.)</t>
+          <t>Letrina institucional (utilizada por un grupo específico, por ejemplo en una escuela o centro de salud)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5495,7 +6895,21 @@
           <t>temp_latrine</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Latrine temporaire (par exemple, installation d’urgence ou temporaire pendant une crise ou une catastrophe)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>مرحاض مؤقت (مثلاً إعداد طارئ أو مؤقت أثناء أزمة أو كارثة)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Letrina temporal (por ejemplo, instalación de emergencia o temporal durante una crisis o desastre)</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>Temporary latrine (e.g., emergency or temporary setup during a crisis or disaster)</t>
@@ -5518,7 +6932,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Autre (précisez)</t>
+          <t>Autre (veuillez préciser)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>أخرى (يرجى التحديد)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Otro (especificar)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5576,7 +7000,21 @@
           <t>excreta</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Avec des excréta visibles en surface</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>مع فضلات ظاهرة على السطح</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Con excretas visibles en la superficie</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>With visible excreta on surface</t>
@@ -5599,17 +7037,17 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Souillures fécales sur la cuvette, les murs ou la porte</t>
+          <t>Traces fécales sur la cuvette, les murs ou la porte</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>لطخات برازية على الحوض والجدران والباب</t>
+          <t>آثار برازية على الوعاء أو الجدران أو الباب</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mancha fecal en cazoleta, paredes o puerta</t>
+          <t>Manchas fecales en la taza, paredes o puerta</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5632,7 +7070,21 @@
           <t>cleaning_materials</t>
         </is>
       </c>
-      <c r="D93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Matériel de nettoyage usagé laissé sur la cuvette</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>مواد تنظيف مستخدمة متروكة على الوعاء</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Materiales de limpieza usados dejados en la taza</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>Used cleaning materials left on pan</t>
@@ -5655,17 +7107,17 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Terre/sable sur le sol, etc.</t>
+          <t>Saleté / sable sur le sol, etc.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>تراب/رمل على الأرضية</t>
+          <t>أوساخ/رمل على الأرض، إلخ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tierra/arena en el suelo</t>
+          <t>Suciedad/arena en el suelo, etc.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5690,7 +7142,17 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Autre (précisez)</t>
+          <t>Autre (veuillez préciser)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>أخرى (يرجى التحديد)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Otro (especificar)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5713,6 +7175,21 @@
           <t>field</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Vers un champ d’épandage ou un puits d’infiltration</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>إلى حقل ترشيح أو حفرة امتصاص</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>A un campo de infiltración o pozo de absorción</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">To a leach field, soak pit </t>
@@ -5733,7 +7210,21 @@
           <t>sewer</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Vers un égout / drain fermé qui mène ailleurs</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>إلى مجرى صرف صحي/مصرف مغلق يؤدي إلى مكان آخر</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>A una alcantarilla/desagüe cerrado que conduce a otro lugar</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>To a sewer/closed drain that leads</t>
@@ -5754,7 +7245,21 @@
           <t>wtp</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Vers une station de traitement des eaux usées</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>إلى محطة معالجة مياه الصرف الصحي</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>A una planta de tratamiento de aguas residuales</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>To a wastewater treatment plant</t>
@@ -5775,7 +7280,21 @@
           <t>waterbody</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Vers un plan d’eau</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>إلى مسطح مائي</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>A un cuerpo de agua</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>To a waterbody</t>
@@ -5796,7 +7315,21 @@
           <t>dk_where</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Vers une destination inconnue</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>إلى مكان غير معروف</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>A un lugar desconocido</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">To don’t know where </t>
@@ -5817,7 +7350,21 @@
           <t>open_drain</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Vers un drain ouvert</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>إلى مصرف مفتوح</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>A un drenaje abierto</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">To an open drain </t>
@@ -5838,7 +7385,21 @@
           <t>waterboday</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Vers un plan d’eau / la surface</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>إلى مسطح مائي/السطح</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>A un cuerpo de agua/superficie</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>To a waterbody/surface</t>
@@ -5861,7 +7422,17 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Autre (précisez)</t>
+          <t>Autre (veuillez préciser)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>أخرى (يرجى التحديد)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Otro (especificar)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5919,7 +7490,21 @@
           <t>cracks</t>
         </is>
       </c>
-      <c r="D105" s="10" t="n"/>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Il y a de grandes fissures, de la corrosion, des déformations ou d’autres dommages visibles au dispositif de confinement</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>توجد تشققات كبيرة أو تآكل أو تشوهات أو أضرار مرئية أخرى في نظام الاحتواء</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Hay grandes grietas, corrosión, deformaciones u otros daños visibles en el sistema de contención</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">There are large cracks, corrosion, deformations or other visible damage to the containment </t>
@@ -5940,7 +7525,21 @@
           <t>malfunction</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n"/>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Dysfonctionnement majeur de l’installation (par exemple système incomplet, tuyaux cassés)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>خلل كبير في المنشأة (مثل نظام غير مكتمل أو أنابيب مكسورة)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Mal funcionamiento grave de la instalación (por ejemplo, sistema incompleto, tuberías rotas)</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">Major malfunction of the installation (e.g. incomplete system, broken pipes) </t>
@@ -5961,7 +7560,21 @@
           <t>ponds</t>
         </is>
       </c>
-      <c r="D107" s="10" t="n"/>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Des mares d’effluents sont visibles au sol / à la surface à l’extérieur du confinement</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>توجد برك من السوائل الخارجة ظاهرة على الأرض/السطح خارج نظام الاحتواء</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Se observan charcos de efluente en el suelo/superficie fuera del sistema de contención</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ponds of effluent are visible on the ground/surface outside the containment </t>
@@ -5982,7 +7595,21 @@
           <t>none</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Aucun de ces problèmes observé</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>لم تتم ملاحظة أي من هذه المشاكل</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>No se observó ninguno de estos problemas</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>None of these issues observed</t>

--- a/inst/resources/tool_obs_latrine_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_latrine_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$67</definedName>
@@ -737,42 +737,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hint::French (fr)</t>
+          <t>hint::French</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>hint::Arabic (ar)</t>
+          <t>hint::Arabic</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>hint::Spanish (sp)</t>
+          <t>hint::Spanish</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>hint::English (en)</t>
+          <t>hint::English</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -3672,82 +3672,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="B145" s="3" t="inlineStr">
         <is>
@@ -3779,30 +3703,28 @@
       <c r="Y145" s="3" t="n"/>
       <c r="Z145" s="3" t="n"/>
     </row>
-    <row r="146"/>
-    <row r="147"/>
     <row r="148">
       <c r="C148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3856,22 +3778,22 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
     </row>
@@ -5022,7 +4944,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -7711,7 +7633,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>English (en)</t>
+          <t>English</t>
         </is>
       </c>
     </row>
